--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/todos.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/todos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>484450.95</v>
+        <v>481726.08</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8134.41</v>
+        <v>8050.32</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12269.22</v>
+        <v>12200.9</v>
       </c>
     </row>
     <row r="5">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9554.700000000001</v>
+        <v>9449.709999999999</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1721.57</v>
+        <v>1712.4</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7015.39</v>
+        <v>7049.15</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>8952.15</v>
+        <v>9018.08</v>
       </c>
     </row>
     <row r="9">
@@ -1004,13 +1004,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>111557.59</v>
+        <v>112379.21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1477-369-CM25</t>
+          <t>550716-15-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1030,17 +1030,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>32064.2</v>
+        <v>6274.95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>550716-15-CM25</t>
+          <t>1477-369-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6283.72</v>
+        <v>32019.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2702-582-CM25</t>
+          <t>2702-583-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1187,13 +1187,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9554.700000000001</v>
+        <v>9605.530000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2702-583-CM25</t>
+          <t>2702-582-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>9554.700000000001</v>
+        <v>9605.530000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1157.21</v>
+        <v>1141.35</v>
       </c>
     </row>
     <row r="15">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1119.88</v>
+        <v>1104.53</v>
       </c>
     </row>
     <row r="16">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>15091.44</v>
+        <v>14888</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1373053-13-CM25</t>
+          <t>307-102-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>8535.68</v>
+        <v>623.76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>307-102-CM25</t>
+          <t>307-103-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>630.53</v>
+        <v>561.39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>307-103-CM25</t>
+          <t>1373053-13-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1579,17 +1579,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>567.47</v>
+        <v>8444.09</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>15179.44</v>
+        <v>15103.88</v>
       </c>
     </row>
     <row r="21">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1803.93</v>
+        <v>1781.82</v>
       </c>
     </row>
     <row r="22">
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>33515.41</v>
+        <v>33211.71</v>
       </c>
     </row>
     <row r="23">
@@ -1858,13 +1858,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6467.76</v>
+        <v>6491.23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>670784-16-CM25</t>
+          <t>1373053-14-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9327.65</v>
+        <v>8304.700000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1373053-14-CM25</t>
+          <t>670784-16-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8315.690000000001</v>
+        <v>9315.32</v>
       </c>
     </row>
     <row r="26">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>32690.79</v>
+        <v>32738.51</v>
       </c>
     </row>
     <row r="27">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>300954.1</v>
+        <v>303167.25</v>
       </c>
     </row>
     <row r="28">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>494472.34</v>
+        <v>500977.05</v>
       </c>
     </row>
     <row r="29">
@@ -2232,13 +2232,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>33557.2</v>
+        <v>33998.64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1217436-22-CM25</t>
+          <t>1217436-21-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>52006.07</v>
+        <v>52355.38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1217436-21-CM25</t>
+          <t>1217436-22-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>52006.07</v>
+        <v>52355.38</v>
       </c>
     </row>
     <row r="32">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2771.9</v>
+        <v>2790.78</v>
       </c>
     </row>
     <row r="33">
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5669438.88</v>
+        <v>5708070.46</v>
       </c>
     </row>
     <row r="34">
@@ -2541,13 +2541,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>73379.10000000001</v>
+        <v>71502.32000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2701-5-CM26</t>
+          <t>574800-1-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Subsecretaria de Relaciones Exteriores</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7446.4</v>
+        <v>63593.52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>574800-1-CM26</t>
+          <t>2701-5-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>65094.36</v>
+        <v>7274.71</v>
       </c>
     </row>
     <row r="37">
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>14794.17</v>
+        <v>14614.26</v>
       </c>
     </row>
     <row r="38">
@@ -2785,13 +2785,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>70420.27</v>
+        <v>69563.86</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>886182-9-SE26</t>
+          <t>1186801-1-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2816,17 +2816,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2839,24 +2839,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>10987.16</v>
+        <v>1239.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1186801-1-CM26</t>
+          <t>886182-9-SE26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2881,17 +2877,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>Universidad de Aysen</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2904,14 +2900,18 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1255.55</v>
+        <v>10849.94</v>
       </c>
     </row>
     <row r="41">
@@ -2972,13 +2972,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1725.99</v>
+        <v>1723.24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>886182-13-CM26</t>
+          <t>606-25-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2998,22 +2998,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>70017.3</v>
+        <v>5919.55</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>606-25-CM26</t>
+          <t>886182-13-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3059,22 +3059,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>Universidad de Aysen</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5917.67</v>
+        <v>70039.59</v>
       </c>
     </row>
     <row r="44">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>46749.59</v>
+        <v>46826.08</v>
       </c>
     </row>
     <row r="45">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7939.54</v>
+        <v>7952.53</v>
       </c>
     </row>
     <row r="46">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>22292.41</v>
+        <v>22149.61</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>544515-1-CM26</t>
+          <t>1153625-3-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3308,17 +3308,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3338,13 +3338,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>51483.72</v>
+        <v>66441.31</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1113381-1-CM26</t>
+          <t>544515-1-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3399,13 +3399,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>72787.33</v>
+        <v>51153.93</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1153625-3-CM26</t>
+          <t>1157285-1-SE26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>Bienestar SSFFAA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3453,20 +3453,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>66869.66</v>
+        <v>50859.94</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1157285-1-SE26</t>
+          <t>1111089-31-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3491,12 +3495,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>62.000.860-5</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bienestar SSFFAA</t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3514,24 +3518,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>51187.84</v>
+        <v>44161.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>786370-1-CM26</t>
+          <t>1113381-1-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3551,22 +3551,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.980.170-9</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3586,13 +3586,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>66573.78</v>
+        <v>72321.07000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1111089-31-CM26</t>
+          <t>786370-1-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3612,17 +3612,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.980.170-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>44446.44</v>
+        <v>66147.32000000001</v>
       </c>
     </row>
     <row r="53">
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>72195.57000000001</v>
+        <v>72653.84</v>
       </c>
     </row>
     <row r="54">
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>10898.37</v>
+        <v>10967.55</v>
       </c>
     </row>
     <row r="55">
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>40240.15</v>
+        <v>40771.06</v>
       </c>
     </row>
     <row r="56">
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>10405.24</v>
+        <v>10558.75</v>
       </c>
     </row>
     <row r="57">
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>51150.89</v>
+        <v>51905.57</v>
       </c>
     </row>
     <row r="58">
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>9418.959999999999</v>
+        <v>9557.92</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>543511-1-CM26</t>
+          <t>626802-3-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4039,17 +4039,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>65.034.169-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>COMISIÓN CHILENA DEL COBRE - COCHILCO</t>
+          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4074,13 +4074,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>9369.639999999999</v>
+        <v>4695.24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>626802-3-CM26</t>
+          <t>543511-1-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4100,17 +4100,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>65.034.169-4</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
+          <t>COMISIÓN CHILENA DEL COBRE - COCHILCO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4135,13 +4135,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4586.19</v>
+        <v>9592.43</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1078191-1-CM26</t>
+          <t>5134-2-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4166,17 +4166,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>Superintendencia de Insolvencia y Reemprendimiento</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>7002.58</v>
+        <v>79768.07000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>772003-2-CM26</t>
+          <t>1477-24-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>60310.91</v>
+        <v>37905.05</v>
       </c>
     </row>
     <row r="63">
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7051.89</v>
+        <v>7256.26</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1477-24-CM26</t>
+          <t>772003-2-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4379,13 +4379,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>36837.49</v>
+        <v>62058.74</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5134-2-CM26</t>
+          <t>1078191-1-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4410,17 +4410,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Superintendencia de Insolvencia y Reemprendimiento</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>77521.47</v>
+        <v>7205.51</v>
       </c>
     </row>
     <row r="66">
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>63090.6</v>
+        <v>62576.9</v>
       </c>
     </row>
     <row r="67">
@@ -4562,13 +4562,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>651.99</v>
+        <v>646.6799999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>606591-4-CM26</t>
+          <t>606591-5-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4623,13 +4623,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>35461.09</v>
+        <v>32901.72</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>606591-5-CM26</t>
+          <t>606591-4-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>32758.58</v>
+        <v>35616.04</v>
       </c>
     </row>
     <row r="70">
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>29725.38</v>
+        <v>29574.68</v>
       </c>
     </row>
     <row r="71">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>47317.95</v>
+        <v>47704.99</v>
       </c>
     </row>
     <row r="72">
@@ -4867,13 +4867,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>48025.7</v>
+        <v>48311.88</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>554892-1-CM26</t>
+          <t>609685-1-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4898,17 +4898,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>53.314.782-8</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>Servicio de Bienestar Dirección de Compras y Contratación Pública</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>61270.68</v>
+        <v>68515.95</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>609685-1-CM26</t>
+          <t>554892-1-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4959,17 +4959,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>53.314.782-8</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar Dirección de Compras y Contratación Pública</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>67943.72</v>
+        <v>61786.7</v>
       </c>
     </row>
     <row r="75">
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1567.15</v>
+        <v>1565.68</v>
       </c>
     </row>
     <row r="76">
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>38222.95</v>
+        <v>38186.96</v>
       </c>
     </row>
     <row r="77">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>8189.65</v>
+        <v>8181.93</v>
       </c>
     </row>
     <row r="78">
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>7229.13</v>
+        <v>7221.2</v>
       </c>
     </row>
     <row r="79">
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>17440.91</v>
+        <v>17394.98</v>
       </c>
     </row>
     <row r="80">
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>10717.31</v>
+        <v>10689.09</v>
       </c>
     </row>
     <row r="81">
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>37813.92</v>
+        <v>37714.34</v>
       </c>
     </row>
     <row r="82">
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1287.11</v>
+        <v>1295.55</v>
       </c>
     </row>
     <row r="83">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>9706.25</v>
+        <v>9730.34</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>544143-2-CM26</t>
+          <t>3378-1719-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5564,22 +5564,22 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5599,13 +5599,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>36312.53</v>
+        <v>17036</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2702-83-CM26</t>
+          <t>307-14-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5630,12 +5630,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5660,13 +5660,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>10661.92</v>
+        <v>646.22</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>307-14-CM26</t>
+          <t>2702-83-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>619.4</v>
+        <v>11123.51</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3378-1719-CM26</t>
+          <t>544143-2-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5747,22 +5747,22 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>16329.07</v>
+        <v>37884.62</v>
       </c>
     </row>
     <row r="88">
@@ -5843,7 +5843,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1035505.11</v>
+        <v>1064847.91</v>
       </c>
     </row>
     <row r="89">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>696818.85</v>
+        <v>716564.4</v>
       </c>
     </row>
     <row r="90">
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>5386172.79</v>
+        <v>5472729.65</v>
       </c>
     </row>
     <row r="91">
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>316975.97</v>
+        <v>317672.53</v>
       </c>
     </row>
     <row r="92">
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1248.69</v>
+        <v>1240.09</v>
       </c>
     </row>
     <row r="93">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>296228.46</v>
+        <v>296262.25</v>
       </c>
     </row>
     <row r="94">
@@ -6221,13 +6221,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>11910.61</v>
+        <v>11922.85</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1078191-2-CM26</t>
+          <t>2701-151-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6252,17 +6252,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>75017.64999999999</v>
+        <v>7784.67</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2701-151-CM26</t>
+          <t>1078191-2-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6313,17 +6313,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>7828.35</v>
+        <v>74599.08</v>
       </c>
     </row>
     <row r="97">
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>10709.95</v>
+        <v>10643.09</v>
       </c>
     </row>
     <row r="98">
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>10181.65</v>
+        <v>10139.47</v>
       </c>
     </row>
     <row r="99">
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>727892.1</v>
+        <v>717480.3100000001</v>
       </c>
     </row>
     <row r="100">
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>192.11</v>
+        <v>189.36</v>
       </c>
     </row>
     <row r="101">
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1222.78</v>
+        <v>1205.28</v>
       </c>
     </row>
     <row r="102">
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>58736.61</v>
+        <v>57482.4</v>
       </c>
     </row>
     <row r="103">
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>36116.05</v>
+        <v>35281.5</v>
       </c>
     </row>
     <row r="104">
@@ -6835,13 +6835,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>37130.21</v>
+        <v>35854.46</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>307-30-CM26</t>
+          <t>603663-54-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6896,13 +6896,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>699.33</v>
+        <v>76156.3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>603663-54-CM26</t>
+          <t>1373053-3-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6957,13 +6957,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>77887.3</v>
+        <v>9257.09</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1373053-3-CM26</t>
+          <t>307-30-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6988,12 +6988,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>9467.5</v>
+        <v>683.78</v>
       </c>
     </row>
     <row r="108">
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>6978.62</v>
+        <v>6777.5</v>
       </c>
     </row>
     <row r="109">
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1268.84</v>
+        <v>1242.65</v>
       </c>
     </row>
     <row r="110">
@@ -7205,7 +7205,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>44895.23</v>
+        <v>44910.95</v>
       </c>
     </row>
     <row r="111">
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>22129.67</v>
+        <v>22072.83</v>
       </c>
     </row>
     <row r="112">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>22129.67</v>
+        <v>22072.83</v>
       </c>
     </row>
     <row r="113">
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>7905.85</v>
+        <v>8109.27</v>
       </c>
     </row>
     <row r="114">
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>10882.75</v>
+        <v>11025.85</v>
       </c>
     </row>
     <row r="115">
@@ -7510,7 +7510,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>7076.23</v>
+        <v>7154.89</v>
       </c>
     </row>
     <row r="116">
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>36649.98</v>
+        <v>36973.69</v>
       </c>
     </row>
     <row r="117">
@@ -7632,7 +7632,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3199.19</v>
+        <v>3227.45</v>
       </c>
     </row>
     <row r="118">
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1159.67</v>
+        <v>1168.85</v>
       </c>
     </row>
     <row r="119">
@@ -7754,7 +7754,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>35478.74</v>
+        <v>35697.47</v>
       </c>
     </row>
     <row r="120">
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>706.84</v>
+        <v>694.21</v>
       </c>
     </row>
     <row r="121">
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>9717.25</v>
+        <v>9595.75</v>
       </c>
     </row>
     <row r="122">
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1282.48</v>
+        <v>1266.44</v>
       </c>
     </row>
     <row r="123">
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>37341.92</v>
+        <v>37633.13</v>
       </c>
     </row>
     <row r="124">
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>31568.74</v>
+        <v>31632.24</v>
       </c>
     </row>
     <row r="125">
@@ -8120,7 +8120,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>10309.17</v>
+        <v>10269.21</v>
       </c>
     </row>
     <row r="126">
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>359291.68</v>
+        <v>361779.55</v>
       </c>
     </row>
     <row r="127">
@@ -8242,7 +8242,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>26438.82</v>
+        <v>26621.89</v>
       </c>
     </row>
     <row r="128">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>8040.16</v>
+        <v>8014.09</v>
       </c>
     </row>
     <row r="129">
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1172.14</v>
+        <v>1161.2</v>
       </c>
     </row>
     <row r="130">
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>10309.17</v>
+        <v>10321.26</v>
       </c>
     </row>
     <row r="131">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>158713.19</v>
+        <v>160141.93</v>
       </c>
     </row>
     <row r="132">
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>9421.290000000001</v>
+        <v>9494.969999999999</v>
       </c>
     </row>
     <row r="133">
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>7250.94</v>
+        <v>7328.32</v>
       </c>
     </row>
     <row r="134">
@@ -8673,7 +8673,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3509.62</v>
+        <v>3547.07</v>
       </c>
     </row>
     <row r="135">
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>709.34</v>
+        <v>717.09</v>
       </c>
     </row>
     <row r="136">
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>10840.59</v>
+        <v>10958.97</v>
       </c>
     </row>
     <row r="137">
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>37372.82</v>
+        <v>37700.6</v>
       </c>
     </row>
     <row r="138">
@@ -8921,13 +8921,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>443479.78</v>
+        <v>449847.9</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>544143-6-CM26</t>
+          <t>1211992-116-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8947,22 +8947,22 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8982,13 +8982,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>37755.97</v>
+        <v>1405.91</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1211992-116-CM26</t>
+          <t>544143-6-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9008,22 +9008,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9043,7 +9043,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1386.01</v>
+        <v>38298.12</v>
       </c>
     </row>
     <row r="141">
@@ -9104,7 +9104,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>31284.27</v>
+        <v>31536.21</v>
       </c>
     </row>
     <row r="142">
@@ -9165,7 +9165,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>4752.04</v>
+        <v>4788.56</v>
       </c>
     </row>
     <row r="143">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>799431.89</v>
+        <v>805575.1800000001</v>
       </c>
     </row>
     <row r="144">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1095642.44</v>
+        <v>1086862.81</v>
       </c>
     </row>
     <row r="145">
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>8019.07</v>
+        <v>8058.6</v>
       </c>
     </row>
     <row r="146">
@@ -9417,7 +9417,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>7227.06</v>
+        <v>7338</v>
       </c>
     </row>
     <row r="147">
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>281162.42</v>
+        <v>286656.49</v>
       </c>
     </row>
     <row r="148">
@@ -9543,7 +9543,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>51084.44</v>
+        <v>51470.7</v>
       </c>
     </row>
     <row r="149">
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>10395.09</v>
+        <v>10377.13</v>
       </c>
     </row>
     <row r="150">
@@ -9665,13 +9665,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>314822.71</v>
+        <v>310935.41</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1495206-5-CM26</t>
+          <t>1477-194-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9696,12 +9696,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9726,13 +9726,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>4036.47</v>
+        <v>36957.96</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1186801-6-CM26</t>
+          <t>1495206-5-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9757,12 +9757,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9787,13 +9787,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1218.29</v>
+        <v>3981.12</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1477-194-CM26</t>
+          <t>1186801-6-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9848,7 +9848,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>37471.82</v>
+        <v>1201.58</v>
       </c>
     </row>
     <row r="154">
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>61479.53</v>
+        <v>60299.47</v>
       </c>
     </row>
     <row r="155">
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>689.64</v>
+        <v>695.87</v>
       </c>
     </row>
     <row r="156">
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>36935.71</v>
+        <v>37065.48</v>
       </c>
     </row>
     <row r="157">
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>10587.58</v>
+        <v>10624.78</v>
       </c>
     </row>
     <row r="158">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>9288.200000000001</v>
+        <v>9324.450000000001</v>
       </c>
     </row>
     <row r="159">
@@ -10214,7 +10214,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>7026.3</v>
+        <v>7073.88</v>
       </c>
     </row>
     <row r="160">
@@ -10279,7 +10279,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>577504.36</v>
+        <v>581414.84</v>
       </c>
     </row>
     <row r="161">
@@ -10340,13 +10340,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1636.26</v>
+        <v>1647.34</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>772003-6-SE26</t>
+          <t>772003-7-SE26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10405,13 +10405,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>154771.17</v>
+        <v>19309.11</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>772003-7-SE26</t>
+          <t>772003-6-SE26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>19346.4</v>
+        <v>154472.86</v>
       </c>
     </row>
     <row r="164">
@@ -10531,7 +10531,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1184.45</v>
+        <v>1177.97</v>
       </c>
     </row>
     <row r="165">
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>10491.33</v>
+        <v>10433.97</v>
       </c>
     </row>
     <row r="166">
@@ -10657,13 +10657,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1406029.91</v>
+        <v>1399224.97</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1477-242-CM26</t>
+          <t>2701-496-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10718,13 +10718,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>36334.65</v>
+        <v>7849.1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2701-496-CM26</t>
+          <t>1477-242-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10779,7 +10779,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>7796.31</v>
+        <v>36580.68</v>
       </c>
     </row>
     <row r="169">
@@ -10840,7 +10840,983 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>36890</v>
+        <v>37139.79</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>670784-9-CM26</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>60.818.000-1</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>10183.13</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>4722-2-CM26</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>65.138.650-0</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>DEFENSORIA PENAL PUBLICA</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>30370.94</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1211992-168-CM26</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>65.192.585-1</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN YUNUS</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="n">
+        <v>1622.04</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>626802-9-CM26</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>65.034.169-4</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>2949.17</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1373053-9-CM26</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>82.174.900-k</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>9583.110000000001</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>3378-4239-CM26</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>61.101.030-3</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>16186.82</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2701-560-CM26</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>69.071.800-6</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>7874.28</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1500781-64-CM26</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>65.260.064-6</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE DEPORTES, CULTURA, RECREACION Y FOMENTO DE HU</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>46630.5</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>550716-10-CM26</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>65.961.370-0</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>7128.25</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>307-82-CM26</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>60.919.000-0</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>699.64</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>670784-10-CM26</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>60.818.000-1</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>10292.87</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1477-270-CM26</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>70.786.200-9</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Corporación de Asistencia Judicial RM</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>37103.35</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>606591-7-CM26</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>60.718.000-8</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>COMISION NACIONAL DE RIEGO</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>31368.75</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1186801-8-CM26</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>60.930.000-0</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>1201.42</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>544143-9-CM26</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>37448.52</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1373053-10-CM26</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>82.174.900-k</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="n">
+        <v>9602.950000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/todos.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/todos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="seguro-colectivo-de- todos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="seguro-colectivo-de- todos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -12186,7 +12186,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15862,7 +15862,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -15988,7 +15988,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -19058,7 +19058,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -19245,7 +19245,7 @@
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -19310,7 +19310,7 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -19497,7 +19497,7 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -20233,7 +20233,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -20672,7 +20672,7 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -20905,7 +20905,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -21027,7 +21027,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21271,7 +21271,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21332,7 +21332,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21393,7 +21393,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21454,7 +21454,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21515,7 +21515,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21637,7 +21637,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21698,7 +21698,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21759,7 +21759,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21820,7 +21820,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/todos.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/todos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M349"/>
+  <dimension ref="A1:M368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -673,11 +673,7 @@
           <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
@@ -734,11 +730,7 @@
           <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
@@ -914,7 +906,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1832,11 +1824,7 @@
           <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
@@ -2836,7 +2824,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1076575-1-CM25</t>
+          <t>561201-3-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2861,17 +2849,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.110.000-2</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE LA JUVENTUD</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2891,13 +2879,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>52696.62</v>
+        <v>42980.68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>561201-3-CM25</t>
+          <t>1076575-1-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2922,17 +2910,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.701.000-3</t>
+          <t>60.110.000-2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+          <t>INSTITUTO NACIONAL DE LA JUVENTUD</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2952,13 +2940,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>42980.68</v>
+        <v>52696.62</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>606591-2-CM25</t>
+          <t>606591-3-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2978,7 +2966,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3013,13 +3001,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>69641.89999999999</v>
+        <v>4974.42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>606591-3-CM25</t>
+          <t>606591-2-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3039,7 +3027,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3074,13 +3062,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4974.42</v>
+        <v>69641.89999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>670784-2-CM25</t>
+          <t>550716-2-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3105,12 +3093,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3135,13 +3123,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8527.16</v>
+        <v>5906.62</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>550716-2-CM25</t>
+          <t>670784-2-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3166,12 +3154,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3196,7 +3184,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>5906.62</v>
+        <v>8527.16</v>
       </c>
     </row>
     <row r="46">
@@ -3385,7 +3373,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1076575-2-CM25</t>
+          <t>2595-72-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3410,17 +3398,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.110.000-2</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE LA JUVENTUD</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3440,13 +3428,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>22882.98</v>
+        <v>10072.41</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2595-72-CM25</t>
+          <t>544143-2-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3471,17 +3459,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3501,13 +3489,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>10072.41</v>
+        <v>31876.29</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>544143-2-CM25</t>
+          <t>1076575-2-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3532,17 +3520,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.110.000-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>INSTITUTO NACIONAL DE LA JUVENTUD</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3562,13 +3550,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>31876.29</v>
+        <v>22882.98</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1477-76-CM25</t>
+          <t>307-15-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3593,12 +3581,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3623,13 +3611,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>29292.08</v>
+        <v>531.36</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>307-15-CM25</t>
+          <t>1477-76-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3654,12 +3642,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3684,7 +3672,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>531.36</v>
+        <v>29292.08</v>
       </c>
     </row>
     <row r="54">
@@ -4239,7 +4227,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>550716-4-CM25</t>
+          <t>1166422-2-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4259,17 +4247,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>61.001.002-4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4294,13 +4282,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>6136.2</v>
+        <v>21450.95</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1166422-2-CM25</t>
+          <t>550716-4-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4320,17 +4308,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.001.002-4</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4355,7 +4343,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>21450.95</v>
+        <v>6136.2</v>
       </c>
     </row>
     <row r="65">
@@ -4910,7 +4898,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2701-291-CM25</t>
+          <t>670784-4-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4935,12 +4923,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4965,13 +4953,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>6803.58</v>
+        <v>8556.65</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>670784-4-CM25</t>
+          <t>2701-291-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4996,12 +4984,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5026,7 +5014,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>8556.65</v>
+        <v>6803.58</v>
       </c>
     </row>
     <row r="76">
@@ -5337,7 +5325,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4700-8-CM25</t>
+          <t>1373053-5-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5362,12 +5350,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>73.362.800-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Consejo de Defensa del Estado</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5392,13 +5380,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>262465.03</v>
+        <v>8122.71</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1373053-5-CM25</t>
+          <t>4700-8-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5423,12 +5411,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>73.362.800-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Consejo de Defensa del Estado</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5453,7 +5441,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>8122.71</v>
+        <v>262465.03</v>
       </c>
     </row>
     <row r="83">
@@ -5947,7 +5935,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>307-40-CM25</t>
+          <t>2702-233-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5972,12 +5960,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6002,13 +5990,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>608.6799999999999</v>
+        <v>9514.190000000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4722-1-CM25</t>
+          <t>3378-4820-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6028,17 +6016,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>65.138.650-0</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6063,13 +6051,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>26827.43</v>
+        <v>15545.51</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3378-4820-CM25</t>
+          <t>4722-1-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6089,17 +6077,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.138.650-0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6124,13 +6112,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>15545.51</v>
+        <v>26827.43</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2702-233-CM25</t>
+          <t>307-40-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6155,12 +6143,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6185,7 +6173,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>9514.190000000001</v>
+        <v>608.6799999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6557,7 +6545,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2701-409-CM25</t>
+          <t>1373053-6-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6582,12 +6570,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6612,13 +6600,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>7002.6</v>
+        <v>8063.6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1373053-6-CM25</t>
+          <t>2701-409-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6643,12 +6631,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6673,13 +6661,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>8063.6</v>
+        <v>7002.6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>670784-6-CM25</t>
+          <t>3378-5109-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6699,17 +6687,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6734,13 +6722,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>8663.24</v>
+        <v>15509.31</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2403-438-CM25</t>
+          <t>670784-6-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6765,12 +6753,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.254.000-k</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENALOLEN</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6795,13 +6783,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>266236.19</v>
+        <v>8663.24</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3378-5109-CM25</t>
+          <t>2403-438-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6821,17 +6809,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>69.254.000-k</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE PENALOLEN</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6856,7 +6844,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>15509.31</v>
+        <v>266236.19</v>
       </c>
     </row>
     <row r="106">
@@ -7289,7 +7277,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1111089-352-CM25</t>
+          <t>2701-473-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7314,12 +7302,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7337,24 +7325,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>173876.66</v>
+        <v>6763.39</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2701-473-CM25</t>
+          <t>1111089-352-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7379,12 +7363,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7402,20 +7386,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>6763.39</v>
+        <v>173876.66</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>670784-7-CM25</t>
+          <t>3378-6239-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7435,17 +7423,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7470,13 +7458,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>8454.799999999999</v>
+        <v>14929.94</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3378-6239-CM25</t>
+          <t>670784-7-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7496,17 +7484,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7531,7 +7519,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>14929.94</v>
+        <v>8454.799999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7720,7 +7708,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3134-257-CM25</t>
+          <t>3134-260-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7775,13 +7763,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>29274.59</v>
+        <v>67597.69</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3134-260-CM25</t>
+          <t>1477-247-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7801,22 +7789,22 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7836,13 +7824,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>67597.69</v>
+        <v>30775.84</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1477-247-CM25</t>
+          <t>1186801-9-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7867,12 +7855,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7897,13 +7885,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>30775.84</v>
+        <v>1104.29</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1186801-9-CM25</t>
+          <t>3134-257-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7923,22 +7911,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7958,7 +7946,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1104.29</v>
+        <v>29274.59</v>
       </c>
     </row>
     <row r="124">
@@ -8761,7 +8749,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>307-64-CM25</t>
+          <t>544143-11-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8786,17 +8774,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8816,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>594.21</v>
+        <v>31703.34</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>544143-11-CM25</t>
+          <t>307-64-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8847,17 +8835,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8877,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>31703.34</v>
+        <v>594.21</v>
       </c>
     </row>
     <row r="139">
@@ -9867,7 +9855,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1373053-10-CM25</t>
+          <t>1373053-11-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9922,13 +9910,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>7801.46</v>
+        <v>7926.61</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1373053-11-CM25</t>
+          <t>1373053-10-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9983,7 +9971,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>7926.61</v>
+        <v>7801.46</v>
       </c>
     </row>
     <row r="157">
@@ -10938,7 +10926,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11034,7 +11022,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1477-369-CM25</t>
+          <t>550716-15-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11054,17 +11042,17 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11089,13 +11077,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>32019.45</v>
+        <v>6274.95</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>550716-15-CM25</t>
+          <t>1477-369-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11115,17 +11103,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11150,7 +11138,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>6274.95</v>
+        <v>32019.45</v>
       </c>
     </row>
     <row r="176">
@@ -11278,7 +11266,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1186801-15-CM25</t>
+          <t>1186801-14-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11333,13 +11321,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1104.53</v>
+        <v>1141.35</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1186801-14-CM25</t>
+          <t>1186801-15-CM25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11394,7 +11382,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1141.35</v>
+        <v>1104.53</v>
       </c>
     </row>
     <row r="180">
@@ -11430,7 +11418,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11461,7 +11449,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>307-103-CM25</t>
+          <t>1373053-13-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11481,17 +11469,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11516,7 +11504,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>561.39</v>
+        <v>8444.09</v>
       </c>
     </row>
     <row r="182">
@@ -11583,7 +11571,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1373053-13-CM25</t>
+          <t>307-103-CM25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11603,17 +11591,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11638,7 +11626,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>8444.09</v>
+        <v>561.39</v>
       </c>
     </row>
     <row r="184">
@@ -11674,7 +11662,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11857,7 +11845,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11888,7 +11876,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1373053-14-CM25</t>
+          <t>670784-16-CM25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11913,12 +11901,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11943,13 +11931,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>8304.700000000001</v>
+        <v>9315.32</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>670784-16-CM25</t>
+          <t>1373053-14-CM25</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11974,12 +11962,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12004,7 +11992,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>9315.32</v>
+        <v>8304.700000000001</v>
       </c>
     </row>
     <row r="190">
@@ -12166,7 +12154,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal de la SVS</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12292,7 +12280,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12353,7 +12341,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12414,7 +12402,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>BIENESTAR DEL CONSEJO DE DEFENSA DEL ESTADO</t>
+          <t>Consejo de Defensa del Estado</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12530,7 +12518,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -12545,7 +12533,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12662,7 +12650,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12723,7 +12711,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Superintendencia de Salud</t>
+          <t>SUPERINTENDENCIA DE SALUD</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12906,7 +12894,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13002,7 +12990,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>886182-13-CM26</t>
+          <t>606-25-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13022,22 +13010,22 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13057,13 +13045,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>70039.59</v>
+        <v>5919.55</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>606-25-CM26</t>
+          <t>886182-13-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13083,22 +13071,22 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13118,13 +13106,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>5919.55</v>
+        <v>70039.59</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1221275-1-CM26</t>
+          <t>2701-18-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13144,17 +13132,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13179,13 +13167,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>46826.08</v>
+        <v>7952.53</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2701-18-CM26</t>
+          <t>1221275-1-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13205,17 +13193,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13240,13 +13228,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>7952.53</v>
+        <v>46826.08</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1153625-3-CM26</t>
+          <t>786370-1-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13266,17 +13254,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>61.980.170-9</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13301,13 +13289,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>66441.31</v>
+        <v>66147.32000000001</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>786370-1-CM26</t>
+          <t>1157285-1-SE26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13327,17 +13315,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.980.170-9</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13355,20 +13343,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>66147.32000000001</v>
+        <v>50859.94</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1157285-1-SE26</t>
+          <t>1111089-31-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13393,12 +13385,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>62.000.860-5</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Bienestar SSFFAA</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13416,24 +13408,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
+      <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>50859.94</v>
+        <v>44161.73</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1111089-31-CM26</t>
+          <t>1113381-1-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13458,17 +13446,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13488,13 +13476,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>44161.73</v>
+        <v>72321.07000000001</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1113381-1-CM26</t>
+          <t>544515-1-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13519,17 +13507,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13549,13 +13537,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>72321.07000000001</v>
+        <v>51153.93</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>544515-1-CM26</t>
+          <t>544515-2-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13610,13 +13598,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>51153.93</v>
+        <v>22149.61</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>544515-2-CM26</t>
+          <t>1153625-3-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13641,17 +13629,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13671,13 +13659,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>22149.61</v>
+        <v>66441.31</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2702-32-CM26</t>
+          <t>785515-1-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13702,12 +13690,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>65.074.471-3</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13732,13 +13720,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>10967.55</v>
+        <v>72653.84</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>785515-1-CM26</t>
+          <t>2702-32-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13763,12 +13751,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>65.074.471-3</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar de los T.T.A.</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13793,7 +13781,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>72653.84</v>
+        <v>10967.55</v>
       </c>
     </row>
     <row r="219">
@@ -13829,7 +13817,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar</t>
+          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13860,7 +13848,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>670784-1-CM26</t>
+          <t>5144-1-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13885,17 +13873,17 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>75.943.840-K</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13915,13 +13903,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>10558.75</v>
+        <v>51905.57</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>5144-1-CM26</t>
+          <t>670784-1-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13946,17 +13934,17 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>75.943.840-K</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Servicio del Bienestar Gobierno Regional Coquimbo</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13976,7 +13964,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>51905.57</v>
+        <v>10558.75</v>
       </c>
     </row>
     <row r="222">
@@ -14043,7 +14031,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>543511-1-CM26</t>
+          <t>626802-3-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14063,17 +14051,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>65.034.169-4</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>COMISIÓN CHILENA DEL COBRE - COCHILCO</t>
+          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14098,13 +14086,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>9592.43</v>
+        <v>4695.24</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>626802-3-CM26</t>
+          <t>543511-1-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14124,17 +14112,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>65.034.169-4</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14159,13 +14147,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>4695.24</v>
+        <v>9592.43</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1078191-1-CM26</t>
+          <t>5134-2-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14190,17 +14178,17 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14220,13 +14208,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>7205.51</v>
+        <v>79768.07000000001</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>550716-1-CM26</t>
+          <t>1477-24-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14246,17 +14234,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14281,13 +14269,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>7256.26</v>
+        <v>37905.05</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>772003-2-CM26</t>
+          <t>550716-1-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14307,17 +14295,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14342,13 +14330,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>62058.74</v>
+        <v>7256.26</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>5134-2-CM26</t>
+          <t>772003-2-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14373,12 +14361,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Superintendencia de Insolvencia y Reemprendimiento</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14403,13 +14391,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>79768.07000000001</v>
+        <v>62058.74</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1477-24-CM26</t>
+          <t>1078191-1-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14434,17 +14422,17 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14464,7 +14452,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>37905.05</v>
+        <v>7205.51</v>
       </c>
     </row>
     <row r="230">
@@ -14744,7 +14732,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Servicio de bienestar UAF</t>
+          <t>UNIDAD DE ANALISIS FINANCIERO</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14805,7 +14793,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Servicio de bienestar del personal del CNTV</t>
+          <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14866,7 +14854,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>COMISIÓN CHILENA DEL COBRE - COCHILCO</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14988,7 +14976,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar Dirección de Compras y Contratación Pública</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15232,7 +15220,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15293,7 +15281,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15354,7 +15342,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15568,7 +15556,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>3378-1719-CM26</t>
+          <t>2702-83-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15588,17 +15576,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15623,13 +15611,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>17036</v>
+        <v>11123.51</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>307-14-CM26</t>
+          <t>544143-2-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15654,17 +15642,17 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15684,13 +15672,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>646.22</v>
+        <v>37884.62</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2702-83-CM26</t>
+          <t>3378-1719-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15710,17 +15698,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15745,13 +15733,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>11123.51</v>
+        <v>17036</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>544143-2-CM26</t>
+          <t>307-14-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15776,17 +15764,17 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15806,7 +15794,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>37884.62</v>
+        <v>646.22</v>
       </c>
     </row>
     <row r="252">
@@ -15842,7 +15830,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15907,7 +15895,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Bienestar</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16464,7 +16452,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -17078,7 +17066,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17170,7 +17158,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2490-79-CM26</t>
+          <t>4973-40-SE26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17185,7 +17173,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -17195,12 +17183,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>69.070.300-9</t>
+          <t>61.202.016-7</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17229,13 +17217,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>44910.95</v>
+        <v>1573308.56</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5482-80-CM26</t>
+          <t>2490-79-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17250,7 +17238,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -17260,12 +17248,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>69.070.500-1</t>
+          <t>69.070.300-9</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUNOA</t>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17283,20 +17271,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>22072.83</v>
+        <v>44910.95</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5482-81-CM26</t>
+          <t>5482-80-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17357,7 +17349,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2701-207-CM26</t>
+          <t>5482-81-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17372,7 +17364,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -17382,12 +17374,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>69.070.500-1</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17412,13 +17404,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>8109.27</v>
+        <v>22072.83</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2702-184-CM26</t>
+          <t>2701-207-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17433,7 +17425,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -17473,13 +17465,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>11025.85</v>
+        <v>8109.27</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>550716-4-CM26</t>
+          <t>2702-184-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17494,22 +17486,22 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17534,13 +17526,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>7154.89</v>
+        <v>11025.85</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1477-108-CM26</t>
+          <t>550716-4-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17555,22 +17547,22 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17595,13 +17587,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>36973.69</v>
+        <v>7154.89</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1495206-1-CM26</t>
+          <t>1477-108-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17626,12 +17618,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17656,13 +17648,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>3227.45</v>
+        <v>36973.69</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1186801-4-CM26</t>
+          <t>1495206-1-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17677,7 +17669,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -17687,12 +17679,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17717,13 +17709,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>1168.85</v>
+        <v>3227.45</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>772003-4-CM26</t>
+          <t>1186801-4-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17738,7 +17730,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -17748,12 +17740,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17778,13 +17770,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>35697.47</v>
+        <v>1168.85</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>307-44-CM26</t>
+          <t>772003-4-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17794,12 +17786,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -17809,12 +17801,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17839,13 +17831,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>694.21</v>
+        <v>35697.47</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1373053-5-CM26</t>
+          <t>307-44-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17860,7 +17852,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -17870,12 +17862,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17900,13 +17892,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>9595.75</v>
+        <v>694.21</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1211992-69-CM26</t>
+          <t>1373053-5-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17926,17 +17918,17 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17961,13 +17953,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1266.44</v>
+        <v>9595.75</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>544143-5-CM26</t>
+          <t>1211992-69-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -17982,27 +17974,27 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -18022,13 +18014,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>37633.13</v>
+        <v>1266.44</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>606591-6-CM26</t>
+          <t>544143-5-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18043,27 +18035,27 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18083,13 +18075,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>31632.24</v>
+        <v>37633.13</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>670784-6-CM26</t>
+          <t>606591-6-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18104,22 +18096,22 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18144,13 +18136,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>10269.21</v>
+        <v>31632.24</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2667-214-CM26</t>
+          <t>670784-6-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18165,7 +18157,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -18175,12 +18167,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VITACURA</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18205,13 +18197,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>361779.55</v>
+        <v>10269.21</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2595-203-CM26</t>
+          <t>2667-214-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18236,17 +18228,17 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18266,13 +18258,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>26621.89</v>
+        <v>361779.55</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2701-300-CM26</t>
+          <t>2595-203-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18287,7 +18279,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -18297,17 +18289,17 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18327,13 +18319,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>8014.09</v>
+        <v>26621.89</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1186801-5-CM26</t>
+          <t>2701-300-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18348,7 +18340,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -18358,12 +18350,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18388,13 +18380,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1161.2</v>
+        <v>8014.09</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>670784-7-CM26</t>
+          <t>1186801-5-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18409,7 +18401,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -18419,12 +18411,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18449,13 +18441,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>10321.26</v>
+        <v>1161.2</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1111089-91-CM26</t>
+          <t>670784-7-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18470,7 +18462,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -18480,12 +18472,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18503,24 +18495,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
+      <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>160141.93</v>
+        <v>10321.26</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1373053-6-CM26</t>
+          <t>1111089-91-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18535,7 +18523,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -18545,12 +18533,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18568,20 +18556,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>9494.969999999999</v>
+        <v>160141.93</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>550716-6-CM26</t>
+          <t>1373053-6-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18596,22 +18588,22 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18636,13 +18628,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>7328.32</v>
+        <v>9494.969999999999</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1495206-3-CM26</t>
+          <t>550716-6-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18662,17 +18654,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18697,13 +18689,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3547.07</v>
+        <v>7328.32</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>307-48-CM26</t>
+          <t>1495206-3-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18713,12 +18705,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -18728,12 +18720,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18758,13 +18750,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>717.09</v>
+        <v>3547.07</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2702-247-CM26</t>
+          <t>307-48-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18789,12 +18781,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18819,13 +18811,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>10958.97</v>
+        <v>717.09</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1477-163-CM26</t>
+          <t>2702-247-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -18840,7 +18832,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -18850,12 +18842,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18880,13 +18872,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>37700.6</v>
+        <v>10958.97</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>544143-6-CM26</t>
+          <t>1477-163-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -18901,7 +18893,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -18911,17 +18903,17 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18941,13 +18933,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>38298.12</v>
+        <v>37700.6</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1211992-116-CM26</t>
+          <t>544143-6-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -18967,22 +18959,22 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -19002,13 +18994,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1405.91</v>
+        <v>38298.12</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>692264-2-SE26</t>
+          <t>1211992-116-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19028,17 +19020,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19056,24 +19048,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
+      <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>449847.9</v>
+        <v>1405.91</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>577258-1-CM26</t>
+          <t>692264-2-SE26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19088,7 +19076,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -19098,17 +19086,17 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>65.017.665-0</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Arica y Parinacota</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19121,20 +19109,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>31536.21</v>
+        <v>449847.9</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1422032-52-CM26</t>
+          <t>577258-1-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19149,7 +19141,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -19159,17 +19151,17 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>65.017.665-0</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19189,13 +19181,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>4788.56</v>
+        <v>31536.21</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1515286-3-SE26</t>
+          <t>1422032-52-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19220,17 +19212,17 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>53.337.014-4</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondo de Bienestar de la Corporación de Fomento </t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19243,24 +19235,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
+      <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>805575.1800000001</v>
+        <v>4788.56</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>5212-57-CM26</t>
+          <t>1515286-3-SE26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19275,27 +19263,27 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>53.337.014-4</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19319,13 +19307,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1086862.81</v>
+        <v>805575.1800000001</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2701-376-CM26</t>
+          <t>5212-57-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19340,7 +19328,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -19350,17 +19338,17 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19373,20 +19361,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>8058.6</v>
+        <v>1086862.81</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>550716-8-CM26</t>
+          <t>2701-376-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19401,7 +19393,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -19411,12 +19403,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19441,13 +19433,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>7338</v>
+        <v>8058.6</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1342-4-SE26</t>
+          <t>550716-8-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19462,7 +19454,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -19472,12 +19464,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>60.109.000-7</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>FONDO DE SOLIDARIDAD E INVERSION SOCIAL</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19495,24 +19487,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
+      <c r="K311" t="inlineStr"/>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>286656.49</v>
+        <v>7338</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1157285-8-CM26</t>
+          <t>1342-4-SE26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -19527,7 +19515,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -19537,12 +19525,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>62.000.860-5</t>
+          <t>60.109.000-7</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Bienestar SSFFAA</t>
+          <t>FONDO DE SOLIDARIDAD E INVERSION SOCIAL</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19560,20 +19548,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>51470.7</v>
+        <v>286656.49</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>670784-8-CM26</t>
+          <t>1157285-8-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -19588,7 +19580,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -19598,12 +19590,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -19628,13 +19620,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>10377.13</v>
+        <v>51470.7</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>4700-10-CM26</t>
+          <t>670784-8-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -19649,7 +19641,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -19659,12 +19651,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>73.362.800-6</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>BIENESTAR DEL CONSEJO DE DEFENSA DEL ESTADO</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -19689,13 +19681,13 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>310935.41</v>
+        <v>10377.13</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1495206-5-CM26</t>
+          <t>4700-10-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -19710,7 +19702,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -19720,12 +19712,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>73.362.800-6</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>Consejo de Defensa del Estado</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -19750,13 +19742,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>3981.12</v>
+        <v>310935.41</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1186801-6-CM26</t>
+          <t>1495206-5-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -19781,12 +19773,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -19811,13 +19803,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1201.58</v>
+        <v>3981.12</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1477-194-CM26</t>
+          <t>1186801-6-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -19842,12 +19834,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -19872,13 +19864,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>36957.96</v>
+        <v>1201.58</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1216062-700-CM26</t>
+          <t>1477-194-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -19893,7 +19885,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -19903,12 +19895,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>71.265.200-4</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Lo Prado</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -19933,13 +19925,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>60299.47</v>
+        <v>36957.96</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>307-54-CM26</t>
+          <t>1216062-700-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -19949,12 +19941,12 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -19964,12 +19956,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>71.265.200-4</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>Corporación Municipal de Lo Prado</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -19994,13 +19986,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>695.87</v>
+        <v>60299.47</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>544143-7-CM26</t>
+          <t>307-54-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -20015,7 +20007,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -20025,17 +20017,17 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20055,13 +20047,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>37065.48</v>
+        <v>695.87</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2702-311-CM26</t>
+          <t>544143-7-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -20086,17 +20078,17 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20116,13 +20108,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>10624.78</v>
+        <v>37065.48</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1373053-8-CM26</t>
+          <t>2702-311-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20137,7 +20129,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -20147,12 +20139,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20177,13 +20169,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>9324.450000000001</v>
+        <v>10624.78</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>545927-3-SE26</t>
+          <t>1373053-8-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20198,7 +20190,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -20208,12 +20200,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>61.212.000-5</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20231,24 +20223,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
+      <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>581414.84</v>
+        <v>9324.450000000001</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1211992-149-CM26</t>
+          <t>550716-9-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20273,12 +20261,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20303,13 +20291,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>1647.34</v>
+        <v>7073.88</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>550716-9-CM26</t>
+          <t>1211992-149-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -20334,12 +20322,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20364,13 +20352,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>7073.88</v>
+        <v>1647.34</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>772003-6-SE26</t>
+          <t>545927-3-SE26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20385,7 +20373,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -20395,12 +20383,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>61.212.000-5</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20429,13 +20417,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>154472.86</v>
+        <v>581414.84</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>772003-7-SE26</t>
+          <t>772003-6-SE26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20494,13 +20482,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>19309.11</v>
+        <v>154472.86</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1186801-7-CM26</t>
+          <t>772003-7-SE26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20515,7 +20503,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -20525,12 +20513,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20548,20 +20536,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1177.97</v>
+        <v>19309.11</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2702-361-CM26</t>
+          <t>1186801-7-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -20586,12 +20578,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20616,13 +20608,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>10433.97</v>
+        <v>1177.97</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1211839-502-SE26</t>
+          <t>2702-361-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -20637,7 +20629,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -20647,12 +20639,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>70.856.400-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -20670,24 +20662,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
+      <c r="K330" t="inlineStr"/>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1399224.97</v>
+        <v>10433.97</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2701-496-CM26</t>
+          <t>1211839-502-SE26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -20702,7 +20690,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -20712,12 +20700,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>70.856.400-1</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20735,20 +20723,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>7849.1</v>
+        <v>1399224.97</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1477-242-CM26</t>
+          <t>2701-496-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -20773,12 +20765,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -20803,13 +20795,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>36580.68</v>
+        <v>7849.1</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>544143-8-CM26</t>
+          <t>1477-242-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -20834,17 +20826,17 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20864,13 +20856,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>37139.79</v>
+        <v>36580.68</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>670784-9-CM26</t>
+          <t>544143-8-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -20880,12 +20872,12 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -20895,17 +20887,17 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20925,13 +20917,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>10183.13</v>
+        <v>37139.79</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>4722-2-CM26</t>
+          <t>670784-9-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -20946,7 +20938,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -20956,12 +20948,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>65.138.650-0</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -20986,13 +20978,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>30370.94</v>
+        <v>10183.13</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>626802-9-CM26</t>
+          <t>4722-2-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -21007,7 +20999,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -21017,12 +21009,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>65.034.169-4</t>
+          <t>65.138.650-0</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -21047,7 +21039,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>2949.17</v>
+        <v>30370.94</v>
       </c>
     </row>
     <row r="337">
@@ -21114,7 +21106,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1373053-9-CM26</t>
+          <t>626802-9-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21129,7 +21121,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -21139,12 +21131,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>65.034.169-4</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21169,13 +21161,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>9583.110000000001</v>
+        <v>2949.17</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>3378-4239-CM26</t>
+          <t>1373053-9-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21190,7 +21182,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -21200,12 +21192,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21230,13 +21222,13 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>16186.82</v>
+        <v>9583.110000000001</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2701-560-CM26</t>
+          <t>3378-4239-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21251,7 +21243,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -21261,12 +21253,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21291,13 +21283,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>7874.28</v>
+        <v>16186.82</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1500781-64-CM26</t>
+          <t>2701-560-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -21322,12 +21314,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>65.260.064-6</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES, CULTURA, RECREACION Y FOMENTO DE HU</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21352,13 +21344,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>46630.5</v>
+        <v>7874.28</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>550716-10-CM26</t>
+          <t>1500781-64-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21373,7 +21365,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -21383,12 +21375,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>65.260.064-6</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES, CULTURA, RECREACION Y FOMENTO DE HU</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21413,13 +21405,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>7128.25</v>
+        <v>46630.5</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>307-82-CM26</t>
+          <t>550716-10-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21439,17 +21431,17 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21474,13 +21466,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>699.64</v>
+        <v>7128.25</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>670784-10-CM26</t>
+          <t>307-82-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -21495,22 +21487,22 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21535,13 +21527,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>10292.87</v>
+        <v>699.64</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1477-270-CM26</t>
+          <t>670784-10-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -21561,17 +21553,17 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -21596,13 +21588,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>37103.35</v>
+        <v>10292.87</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>606591-7-CM26</t>
+          <t>1477-270-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -21622,17 +21614,17 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21657,13 +21649,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>31368.75</v>
+        <v>37103.35</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1186801-8-CM26</t>
+          <t>606591-7-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -21678,22 +21670,22 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21718,13 +21710,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>1201.42</v>
+        <v>31368.75</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>544143-9-CM26</t>
+          <t>1186801-8-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -21739,7 +21731,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -21749,17 +21741,17 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21779,13 +21771,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>37448.52</v>
+        <v>1201.42</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1373053-10-CM26</t>
+          <t>544143-9-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -21810,17 +21802,17 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21840,7 +21832,1166 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
+        <v>37448.52</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>1373053-10-CM26</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>82.174.900-k</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="n">
         <v>9602.950000000001</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>1211992-189-CM26</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>65.192.585-1</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN YUNUS</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M351" s="2" t="n">
+        <v>1633.34</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>307-88-CM26</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>60.919.000-0</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M352" s="2" t="n">
+        <v>685.88</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>4722-3-CM26</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>65.138.650-0</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>DEFENSORIA PENAL PUBLICA</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M353" s="2" t="n">
+        <v>30024.39</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>786370-3-CM26</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>61.980.170-9</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="n">
+        <v>90796.42999999999</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2701-649-CM26</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>69.071.800-6</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M355" s="2" t="n">
+        <v>7644.2</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2702-443-CM26</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>69.071.800-6</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M356" s="2" t="n">
+        <v>10270.43</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>550716-12-CM26</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>65.961.370-0</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M357" s="2" t="n">
+        <v>6943.58</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2702-464-CM26</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>69.071.800-6</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M358" s="2" t="n">
+        <v>10413.64</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>1186801-10-CM26</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>60.930.000-0</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M359" s="2" t="n">
+        <v>4681.22</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>307-95-CM26</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>60.919.000-0</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M360" s="2" t="n">
+        <v>667.67</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>307-96-CM26</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>60.919.000-0</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M361" s="2" t="n">
+        <v>667.67</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>307-97-CM26</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>60.919.000-0</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="n">
+        <v>667.67</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>307-98-CM26</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>60.919.000-0</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="n">
+        <v>667.67</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2701-675-CM26</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>69.071.800-6</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="n">
+        <v>7594.58</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2701-676-CM26</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>69.071.800-6</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="n">
+        <v>7594.58</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2701-677-CM26</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>69.071.800-6</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="n">
+        <v>7594.58</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1477-295-CM26</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>70.786.200-9</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Corporación de Asistencia Judicial RM</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="n">
+        <v>35397.27</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>1495206-6-CM26</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="n">
+        <v>20926.2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/todos.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/todos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M372"/>
+  <dimension ref="A1:M374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3297,7 +3297,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>550716-2-CM25</t>
+          <t>670784-2-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3356,13 +3356,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>5906.62</v>
+        <v>8527.16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>670784-2-CM25</t>
+          <t>550716-2-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8527.16</v>
+        <v>5906.62</v>
       </c>
     </row>
     <row r="47">
@@ -5637,7 +5637,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1211992-94-CM25</t>
+          <t>544143-6-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5657,22 +5657,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5696,13 +5696,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2018.28</v>
+        <v>32668.39</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>544143-6-CM25</t>
+          <t>1211992-94-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5722,22 +5722,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5761,7 +5761,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>32668.39</v>
+        <v>2018.28</v>
       </c>
     </row>
     <row r="83">
@@ -5962,7 +5962,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1186801-5-CM25</t>
+          <t>2701-360-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6021,13 +6021,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1072.05</v>
+        <v>6907.56</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2701-360-CM25</t>
+          <t>1186801-5-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6086,7 +6086,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>6907.56</v>
+        <v>1072.05</v>
       </c>
     </row>
     <row r="88">
@@ -6742,7 +6742,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1157285-10-CM25</t>
+          <t>3378-5108-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6762,17 +6762,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>62.000.860-5</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6801,13 +6801,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>45047.81</v>
+        <v>15869.12</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3378-5108-CM25</t>
+          <t>1157285-10-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6866,7 +6866,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>15869.12</v>
+        <v>45047.81</v>
       </c>
     </row>
     <row r="100">
@@ -8172,7 +8172,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3378-6241-CM25</t>
+          <t>550716-10-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8231,13 +8231,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>15046.09</v>
+        <v>6102.03</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>550716-10-CM25</t>
+          <t>3378-6241-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>6102.03</v>
+        <v>15046.09</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3134-257-CM25</t>
+          <t>3134-260-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8361,13 +8361,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>29274.59</v>
+        <v>67597.69</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3134-260-CM25</t>
+          <t>1477-247-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8387,22 +8387,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8426,13 +8426,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>67597.69</v>
+        <v>30775.84</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1477-247-CM25</t>
+          <t>1186801-9-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8491,13 +8491,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>30775.84</v>
+        <v>1104.29</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1186801-9-CM25</t>
+          <t>3134-257-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8517,22 +8517,22 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8556,7 +8556,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1104.29</v>
+        <v>29274.59</v>
       </c>
     </row>
     <row r="126">
@@ -8822,7 +8822,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2702-382-CM25</t>
+          <t>1373053-9-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8881,13 +8881,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>9183.23</v>
+        <v>7776.79</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1373053-9-CM25</t>
+          <t>2702-382-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>7776.79</v>
+        <v>9183.23</v>
       </c>
     </row>
     <row r="132">
@@ -9862,7 +9862,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>550716-13-CM25</t>
+          <t>2701-636-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9882,17 +9882,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9921,13 +9921,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>6074.37</v>
+        <v>6875.85</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2701-636-CM25</t>
+          <t>550716-13-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9947,17 +9947,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>6875.85</v>
+        <v>6074.37</v>
       </c>
     </row>
     <row r="148">
@@ -14022,7 +14022,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2701-18-CM26</t>
+          <t>1221275-1-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -14042,17 +14042,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>7952.53</v>
+        <v>46826.08</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1221275-1-CM26</t>
+          <t>2701-18-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -14107,17 +14107,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -14146,13 +14146,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>46826.08</v>
+        <v>7952.53</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>786370-1-CM26</t>
+          <t>1153625-3-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14172,17 +14172,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.980.170-9</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -14211,13 +14211,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>66147.32000000001</v>
+        <v>66441.31</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1157285-1-SE26</t>
+          <t>544515-2-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14242,17 +14242,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>62.000.860-5</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -14276,13 +14276,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>50859.94</v>
+        <v>22149.61</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1111089-31-CM26</t>
+          <t>544515-1-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14307,17 +14307,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -14341,13 +14341,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>44161.73</v>
+        <v>51153.93</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1113381-1-CM26</t>
+          <t>1157285-1-SE26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14372,17 +14372,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -14406,13 +14406,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>72321.07000000001</v>
+        <v>50859.94</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>544515-1-CM26</t>
+          <t>1111089-31-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14437,17 +14437,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -14471,13 +14471,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>51153.93</v>
+        <v>44161.73</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>544515-2-CM26</t>
+          <t>786370-1-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14497,22 +14497,22 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>61.980.170-9</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -14536,13 +14536,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>22149.61</v>
+        <v>66147.32000000001</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1153625-3-CM26</t>
+          <t>1113381-1-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14567,17 +14567,17 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -14601,7 +14601,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>66441.31</v>
+        <v>72321.07000000001</v>
       </c>
     </row>
     <row r="219">
@@ -14802,7 +14802,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5144-1-CM26</t>
+          <t>670784-1-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14827,17 +14827,17 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>75.943.840-K</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14861,13 +14861,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>51905.57</v>
+        <v>10558.75</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>670784-1-CM26</t>
+          <t>5144-1-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14892,17 +14892,17 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>75.943.840-K</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14926,7 +14926,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>10558.75</v>
+        <v>51905.57</v>
       </c>
     </row>
     <row r="224">
@@ -14997,7 +14997,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>626802-3-CM26</t>
+          <t>543511-1-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>65.034.169-4</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -15056,13 +15056,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>4695.24</v>
+        <v>9592.43</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>543511-1-CM26</t>
+          <t>626802-3-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15082,17 +15082,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>65.034.169-4</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -15121,13 +15121,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>9592.43</v>
+        <v>4695.24</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5134-2-CM26</t>
+          <t>1078191-1-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15152,17 +15152,17 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -15186,13 +15186,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>79768.07000000001</v>
+        <v>7205.51</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1477-24-CM26</t>
+          <t>772003-2-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15217,12 +15217,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -15251,13 +15251,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>37905.05</v>
+        <v>62058.74</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>550716-1-CM26</t>
+          <t>5134-2-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15277,17 +15277,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -15316,13 +15316,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>7256.26</v>
+        <v>79768.07000000001</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>772003-2-CM26</t>
+          <t>1477-24-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15347,12 +15347,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -15381,13 +15381,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>62058.74</v>
+        <v>37905.05</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1078191-1-CM26</t>
+          <t>550716-1-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15407,22 +15407,22 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -15446,7 +15446,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>7205.51</v>
+        <v>7256.26</v>
       </c>
     </row>
     <row r="232">
@@ -15907,7 +15907,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>554892-1-CM26</t>
+          <t>609685-1-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15932,17 +15932,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>53.314.782-8</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15966,13 +15966,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>61786.7</v>
+        <v>68515.95</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>609685-1-CM26</t>
+          <t>554892-1-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15997,17 +15997,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>53.314.782-8</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -16031,13 +16031,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>68515.95</v>
+        <v>61786.7</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1211992-22-CM26</t>
+          <t>2701-85-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16057,17 +16057,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -16096,7 +16096,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1565.68</v>
+        <v>8181.93</v>
       </c>
     </row>
     <row r="242">
@@ -16167,7 +16167,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2701-85-CM26</t>
+          <t>1211992-22-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16187,17 +16187,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16226,7 +16226,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>8181.93</v>
+        <v>1565.68</v>
       </c>
     </row>
     <row r="244">
@@ -16622,7 +16622,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>307-14-CM26</t>
+          <t>3378-1719-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16642,17 +16642,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16681,13 +16681,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>646.22</v>
+        <v>17036</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2702-83-CM26</t>
+          <t>307-14-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16712,12 +16712,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16746,13 +16746,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>11123.51</v>
+        <v>646.22</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>3378-1719-CM26</t>
+          <t>2702-83-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16772,17 +16772,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16811,7 +16811,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>17036</v>
+        <v>11123.51</v>
       </c>
     </row>
     <row r="253">
@@ -16882,7 +16882,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>574800-3-SE26</t>
+          <t>575437-3-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16907,12 +16907,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>60.805.312-3</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16941,13 +16941,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>716564.4</v>
+        <v>1064847.91</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>575437-3-CM26</t>
+          <t>574800-3-SE26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16972,12 +16972,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>60.805.312-3</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1064847.91</v>
+        <v>716564.4</v>
       </c>
     </row>
     <row r="256">
@@ -18767,7 +18767,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1477-108-CM26</t>
+          <t>1495206-1-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18792,12 +18792,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18826,13 +18826,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>36973.69</v>
+        <v>3227.45</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1495206-1-CM26</t>
+          <t>1477-108-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18857,12 +18857,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18891,7 +18891,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>3227.45</v>
+        <v>36973.69</v>
       </c>
     </row>
     <row r="285">
@@ -19742,7 +19742,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1395481-3-SE26</t>
+          <t>1395481-2-SE26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19801,13 +19801,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>257795.23</v>
+        <v>117272.9</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1111089-91-CM26</t>
+          <t>1395481-3-SE26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19832,12 +19832,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.908.116-3</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19866,13 +19866,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>160141.93</v>
+        <v>257795.23</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1395481-2-SE26</t>
+          <t>1111089-91-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19897,12 +19897,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>60.908.116-3</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19931,7 +19931,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>117272.9</v>
+        <v>160141.93</v>
       </c>
     </row>
     <row r="301">
@@ -21692,7 +21692,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>545927-3-SE26</t>
+          <t>1211992-149-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21717,12 +21717,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.212.000-5</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21751,13 +21751,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>581414.84</v>
+        <v>1647.34</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1211992-149-CM26</t>
+          <t>550716-9-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21782,12 +21782,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21816,13 +21816,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1647.34</v>
+        <v>7073.88</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>550716-9-CM26</t>
+          <t>545927-3-SE26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21847,12 +21847,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>61.212.000-5</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21881,7 +21881,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>7073.88</v>
+        <v>581414.84</v>
       </c>
     </row>
     <row r="331">
@@ -22537,7 +22537,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>626802-9-CM26</t>
+          <t>1211992-168-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22557,17 +22557,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>65.034.169-4</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22596,13 +22596,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2949.17</v>
+        <v>1622.04</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1211992-168-CM26</t>
+          <t>626802-9-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22622,17 +22622,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>65.034.169-4</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22661,13 +22661,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1622.04</v>
+        <v>2949.17</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1373053-9-CM26</t>
+          <t>846677-2-SE26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22682,22 +22682,22 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.979.950-k</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Superintendencia del Medio Ambiente</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22726,13 +22726,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>9583.110000000001</v>
+        <v>104140.14</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>3378-4239-CM26</t>
+          <t>1373053-9-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22747,7 +22747,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -22757,12 +22757,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -22791,13 +22791,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>16186.82</v>
+        <v>9583.110000000001</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2701-560-CM26</t>
+          <t>3378-4239-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22812,7 +22812,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -22822,12 +22822,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22856,13 +22856,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>7874.28</v>
+        <v>16186.82</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1500781-64-CM26</t>
+          <t>2701-560-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22887,12 +22887,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>65.260.064-6</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES, CULTURA, RECREACION Y FOMENTO DE HU</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -22921,13 +22921,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>46630.5</v>
+        <v>7874.28</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>550716-10-CM26</t>
+          <t>1500781-64-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22942,22 +22942,22 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>65.260.064-6</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES, CULTURA, RECREACION Y FOMENTO DE HU</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>7128.25</v>
+        <v>46630.5</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>307-82-CM26</t>
+          <t>550716-10-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -23012,17 +23012,17 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -23051,13 +23051,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>699.64</v>
+        <v>7128.25</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>670784-10-CM26</t>
+          <t>307-82-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -23072,22 +23072,22 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -23116,13 +23116,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>10292.87</v>
+        <v>699.64</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1477-270-CM26</t>
+          <t>670784-10-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -23142,17 +23142,17 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -23181,13 +23181,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>37103.35</v>
+        <v>10292.87</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>606591-7-CM26</t>
+          <t>1477-270-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23207,17 +23207,17 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -23246,13 +23246,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>31368.75</v>
+        <v>37103.35</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1186801-8-CM26</t>
+          <t>606591-7-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23267,22 +23267,22 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -23311,13 +23311,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>1201.42</v>
+        <v>31368.75</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>544143-9-CM26</t>
+          <t>1186801-8-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23332,7 +23332,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -23342,17 +23342,17 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -23376,13 +23376,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>37448.52</v>
+        <v>1201.42</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1373053-10-CM26</t>
+          <t>544143-9-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -23407,17 +23407,17 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -23441,13 +23441,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>9602.950000000001</v>
+        <v>37448.52</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1211992-189-CM26</t>
+          <t>1373053-10-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23457,12 +23457,12 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -23472,12 +23472,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -23506,13 +23506,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1633.34</v>
+        <v>9602.950000000001</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>307-88-CM26</t>
+          <t>1211992-189-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23527,7 +23527,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -23537,12 +23537,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23571,13 +23571,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>685.88</v>
+        <v>1633.34</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>4722-3-CM26</t>
+          <t>307-88-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23592,7 +23592,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -23602,12 +23602,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>65.138.650-0</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23636,13 +23636,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>30024.39</v>
+        <v>685.88</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>786370-3-CM26</t>
+          <t>4722-3-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23657,22 +23657,22 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.980.170-9</t>
+          <t>65.138.650-0</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23701,13 +23701,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>90796.42999999999</v>
+        <v>30024.39</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2701-649-CM26</t>
+          <t>786370-3-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23722,22 +23722,22 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.980.170-9</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23766,7 +23766,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>7644.2</v>
+        <v>90796.42999999999</v>
       </c>
     </row>
     <row r="360">
@@ -23837,7 +23837,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>550716-12-CM26</t>
+          <t>2701-649-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23852,7 +23852,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -23862,12 +23862,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23896,13 +23896,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>6943.58</v>
+        <v>7644.2</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2702-464-CM26</t>
+          <t>558338-4-SE26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23917,7 +23917,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -23927,12 +23927,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23961,13 +23961,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>10413.64</v>
+        <v>306084.36</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1186801-10-CM26</t>
+          <t>550716-12-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -24026,13 +24026,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>4681.22</v>
+        <v>6943.58</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2701-675-CM26</t>
+          <t>2702-464-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -24047,7 +24047,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -24091,13 +24091,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>7594.58</v>
+        <v>10413.64</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>307-98-CM26</t>
+          <t>1186801-10-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -24112,7 +24112,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -24122,12 +24122,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -24156,13 +24156,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>667.67</v>
+        <v>4681.22</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2701-676-CM26</t>
+          <t>307-95-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24187,12 +24187,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24221,7 +24221,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>7594.58</v>
+        <v>667.67</v>
       </c>
     </row>
     <row r="367">
@@ -24292,7 +24292,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>307-95-CM26</t>
+          <t>307-97-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24357,7 +24357,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>307-97-CM26</t>
+          <t>307-98-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -24422,7 +24422,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2701-677-CM26</t>
+          <t>2701-675-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -24487,7 +24487,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1477-295-CM26</t>
+          <t>2701-676-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -24502,7 +24502,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -24512,12 +24512,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -24546,71 +24546,201 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>35397.27</v>
+        <v>7594.58</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
+          <t>2701-677-CM26</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>69.071.800-6</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M372" s="2" t="n">
+        <v>7594.58</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>1477-295-CM26</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>70.786.200-9</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Corporación de Asistencia Judicial RM</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="n">
+        <v>35397.27</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
           <t>1495206-6-CM26</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>2239-12-LR23</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
+      <c r="D374" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
         <is>
           <t>61.981.340-5</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr">
+      <c r="G374" t="inlineStr">
         <is>
           <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I372" t="inlineStr">
-        <is>
-          <t>BCI SEGUROS VIDA S A</t>
-        </is>
-      </c>
-      <c r="J372" t="inlineStr">
-        <is>
-          <t>96.573.600-K</t>
-        </is>
-      </c>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
-      <c r="L372" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M372" s="2" t="n">
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="n">
         <v>20926.2</v>
       </c>
     </row>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/todos.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/todos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M374"/>
+  <dimension ref="A1:M387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1091,7 +1091,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>886182-4-CM25</t>
+          <t>553925-1-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1111,22 +1111,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>41777.34</v>
+        <v>62334.55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1166422-1-CM25</t>
+          <t>886182-4-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.001.002-4</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1215,13 +1215,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>19405.65</v>
+        <v>41777.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>553925-1-CM25</t>
+          <t>1166422-1-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>61.001.002-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>62334.55</v>
+        <v>19405.65</v>
       </c>
     </row>
     <row r="14">
@@ -1611,7 +1611,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2702-27-CM25</t>
+          <t>543511-2-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>8899.790000000001</v>
+        <v>7370.75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>543511-2-CM25</t>
+          <t>2702-27-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7370.75</v>
+        <v>8899.790000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>544515-1-CM25</t>
+          <t>544515-2-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1800,13 +1800,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>39259.39</v>
+        <v>17002.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>544515-2-CM25</t>
+          <t>544515-1-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>17002.1</v>
+        <v>39259.39</v>
       </c>
     </row>
     <row r="23">
@@ -2907,7 +2907,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2701-124-CM25</t>
+          <t>1273563-1-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>62.000.740-4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>6690.04</v>
+        <v>36836.51</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1273563-1-CM25</t>
+          <t>2701-124-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2997,12 +2997,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>62.000.740-4</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>36836.51</v>
+        <v>6690.04</v>
       </c>
     </row>
     <row r="41">
@@ -3167,7 +3167,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>606591-3-CM25</t>
+          <t>606591-2-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3226,13 +3226,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4974.42</v>
+        <v>69641.89999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>606591-2-CM25</t>
+          <t>606591-3-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>69641.89999999999</v>
+        <v>4974.42</v>
       </c>
     </row>
     <row r="45">
@@ -3622,7 +3622,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2595-72-CM25</t>
+          <t>544143-2-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3681,13 +3681,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>10072.41</v>
+        <v>31876.29</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>544143-2-CM25</t>
+          <t>1076575-2-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3712,17 +3712,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.110.000-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>INSTITUTO NACIONAL DE LA JUVENTUD</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>31876.29</v>
+        <v>22882.98</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1076575-2-CM25</t>
+          <t>2595-72-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3777,17 +3777,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.110.000-2</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE LA JUVENTUD</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>22882.98</v>
+        <v>10072.41</v>
       </c>
     </row>
     <row r="53">
@@ -4337,7 +4337,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2701-191-CM25</t>
+          <t>2702-123-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4396,13 +4396,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6964.44</v>
+        <v>9570.76</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2702-123-CM25</t>
+          <t>2701-191-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9570.76</v>
+        <v>6964.44</v>
       </c>
     </row>
     <row r="63">
@@ -4792,7 +4792,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>307-21-CM25</t>
+          <t>553925-2-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4817,12 +4817,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4851,13 +4851,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>538.7</v>
+        <v>22512.79</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>553925-2-CM25</t>
+          <t>307-21-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4882,12 +4882,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>22512.79</v>
+        <v>538.7</v>
       </c>
     </row>
     <row r="70">
@@ -5637,7 +5637,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>544143-6-CM25</t>
+          <t>1211992-94-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5657,22 +5657,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5696,13 +5696,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>32668.39</v>
+        <v>2018.28</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1211992-94-CM25</t>
+          <t>544143-6-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5722,22 +5722,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5761,7 +5761,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2018.28</v>
+        <v>32668.39</v>
       </c>
     </row>
     <row r="83">
@@ -5962,7 +5962,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2701-360-CM25</t>
+          <t>1186801-5-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6021,13 +6021,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>6907.56</v>
+        <v>1072.05</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1186801-5-CM25</t>
+          <t>2701-360-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6086,7 +6086,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1072.05</v>
+        <v>6907.56</v>
       </c>
     </row>
     <row r="88">
@@ -6482,7 +6482,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3378-4820-CM25</t>
+          <t>4722-1-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6502,17 +6502,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.138.650-0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6541,13 +6541,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>15545.51</v>
+        <v>26827.43</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4722-1-CM25</t>
+          <t>307-40-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6572,12 +6572,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>65.138.650-0</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6606,13 +6606,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>26827.43</v>
+        <v>608.6799999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>307-40-CM25</t>
+          <t>3378-4820-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6632,17 +6632,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>608.6799999999999</v>
+        <v>15545.51</v>
       </c>
     </row>
     <row r="97">
@@ -7197,7 +7197,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3378-5109-CM25</t>
+          <t>670784-6-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7217,17 +7217,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7256,13 +7256,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>15509.31</v>
+        <v>8663.24</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>670784-6-CM25</t>
+          <t>2403-438-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>69.254.000-k</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>I MUNICIPALIDAD DE PENALOLEN</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7321,13 +7321,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>8663.24</v>
+        <v>266236.19</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2403-438-CM25</t>
+          <t>3378-5109-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7347,17 +7347,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.254.000-k</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENALOLEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7386,7 +7386,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>266236.19</v>
+        <v>15509.31</v>
       </c>
     </row>
     <row r="108">
@@ -7847,7 +7847,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2701-473-CM25</t>
+          <t>1111089-352-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7906,13 +7906,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>6763.39</v>
+        <v>173876.66</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1111089-352-CM25</t>
+          <t>2701-473-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>173876.66</v>
+        <v>6763.39</v>
       </c>
     </row>
     <row r="117">
@@ -8172,7 +8172,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>550716-10-CM25</t>
+          <t>3378-6241-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8231,13 +8231,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>6102.03</v>
+        <v>15046.09</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3378-6241-CM25</t>
+          <t>550716-10-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>15046.09</v>
+        <v>6102.03</v>
       </c>
     </row>
     <row r="122">
@@ -8367,7 +8367,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1477-247-CM25</t>
+          <t>3134-257-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8387,22 +8387,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>30775.84</v>
+        <v>29274.59</v>
       </c>
     </row>
     <row r="124">
@@ -8497,7 +8497,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3134-257-CM25</t>
+          <t>1477-247-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8517,22 +8517,22 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8556,7 +8556,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>29274.59</v>
+        <v>30775.84</v>
       </c>
     </row>
     <row r="126">
@@ -9212,7 +9212,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>670784-8-CM25</t>
+          <t>2595-444-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -9271,13 +9271,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>8490.299999999999</v>
+        <v>12914</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2595-444-CM25</t>
+          <t>670784-8-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9302,17 +9302,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>12914</v>
+        <v>8490.299999999999</v>
       </c>
     </row>
     <row r="138">
@@ -9407,7 +9407,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>544143-11-CM25</t>
+          <t>307-64-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9432,17 +9432,17 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9466,13 +9466,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>31703.34</v>
+        <v>594.21</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>307-64-CM25</t>
+          <t>544143-11-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9497,17 +9497,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>594.21</v>
+        <v>31703.34</v>
       </c>
     </row>
     <row r="141">
@@ -10577,7 +10577,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1373053-10-CM25</t>
+          <t>1373053-11-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10636,13 +10636,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>7801.46</v>
+        <v>7926.61</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1373053-11-CM25</t>
+          <t>1373053-10-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>7926.61</v>
+        <v>7801.46</v>
       </c>
     </row>
     <row r="159">
@@ -10902,7 +10902,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1186801-13-CM25</t>
+          <t>670784-11-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10961,13 +10961,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1108.64</v>
+        <v>8683.26</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>670784-11-CM25</t>
+          <t>1186801-13-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10992,12 +10992,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11026,7 +11026,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>8683.26</v>
+        <v>1108.64</v>
       </c>
     </row>
     <row r="164">
@@ -12072,7 +12072,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1186801-15-CM25</t>
+          <t>1186801-14-CM25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12131,13 +12131,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1104.53</v>
+        <v>1141.35</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1186801-14-CM25</t>
+          <t>1186801-15-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12196,7 +12196,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1141.35</v>
+        <v>1104.53</v>
       </c>
     </row>
     <row r="182">
@@ -12267,7 +12267,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>307-102-CM25</t>
+          <t>1373053-13-CM25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12292,12 +12292,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12326,7 +12326,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>623.76</v>
+        <v>8444.09</v>
       </c>
     </row>
     <row r="184">
@@ -12397,7 +12397,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1373053-13-CM25</t>
+          <t>307-102-CM25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12422,12 +12422,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12456,7 +12456,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>8444.09</v>
+        <v>623.76</v>
       </c>
     </row>
     <row r="186">
@@ -12722,7 +12722,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>670784-16-CM25</t>
+          <t>1373053-14-CM25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12747,12 +12747,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>9315.32</v>
+        <v>8304.700000000001</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1373053-14-CM25</t>
+          <t>670784-16-CM25</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12812,12 +12812,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12846,7 +12846,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>8304.700000000001</v>
+        <v>9315.32</v>
       </c>
     </row>
     <row r="192">
@@ -12982,7 +12982,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>598002-22-SE25</t>
+          <t>544143-15-CM25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13002,22 +13002,22 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>60.810.001-6</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -13041,13 +13041,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>500977.05</v>
+        <v>33998.64</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>544143-15-CM25</t>
+          <t>598002-22-SE25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -13067,22 +13067,22 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.810.001-6</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -13106,13 +13106,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>33998.64</v>
+        <v>500977.05</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1217436-21-CM25</t>
+          <t>1217436-22-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13177,7 +13177,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1217436-22-CM25</t>
+          <t>1217436-21-CM25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -14347,7 +14347,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1157285-1-SE26</t>
+          <t>786370-1-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14367,17 +14367,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>62.000.860-5</t>
+          <t>61.980.170-9</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
+          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14406,7 +14406,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>50859.94</v>
+        <v>66147.32000000001</v>
       </c>
     </row>
     <row r="216">
@@ -14477,7 +14477,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>786370-1-CM26</t>
+          <t>1157285-1-SE26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14497,17 +14497,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.980.170-9</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14536,7 +14536,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>66147.32000000001</v>
+        <v>50859.94</v>
       </c>
     </row>
     <row r="218">
@@ -14802,7 +14802,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>670784-1-CM26</t>
+          <t>1373053-1-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14827,12 +14827,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14861,13 +14861,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>10558.75</v>
+        <v>9557.92</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>5144-1-CM26</t>
+          <t>670784-1-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14892,17 +14892,17 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>75.943.840-K</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14926,13 +14926,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>51905.57</v>
+        <v>10558.75</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1373053-1-CM26</t>
+          <t>5144-1-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14957,17 +14957,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>75.943.840-K</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14991,13 +14991,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>9557.92</v>
+        <v>51905.57</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>543511-1-CM26</t>
+          <t>626802-3-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>65.034.169-4</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -15056,13 +15056,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>9592.43</v>
+        <v>4695.24</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>626802-3-CM26</t>
+          <t>543511-1-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15082,17 +15082,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>65.034.169-4</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -15121,13 +15121,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>4695.24</v>
+        <v>9592.43</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1078191-1-CM26</t>
+          <t>5134-2-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15152,17 +15152,17 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -15186,13 +15186,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>7205.51</v>
+        <v>79768.07000000001</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>772003-2-CM26</t>
+          <t>1477-24-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15217,12 +15217,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -15251,13 +15251,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>62058.74</v>
+        <v>37905.05</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5134-2-CM26</t>
+          <t>550716-1-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15277,17 +15277,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -15316,13 +15316,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>79768.07000000001</v>
+        <v>7256.26</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1477-24-CM26</t>
+          <t>772003-2-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15347,12 +15347,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -15381,13 +15381,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>37905.05</v>
+        <v>62058.74</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>550716-1-CM26</t>
+          <t>1078191-1-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15407,22 +15407,22 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -15446,13 +15446,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>7256.26</v>
+        <v>7205.51</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>553883-1-CM26</t>
+          <t>307-11-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15477,17 +15477,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -15511,13 +15511,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>62576.9</v>
+        <v>646.6799999999999</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>307-11-CM26</t>
+          <t>553883-1-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15542,17 +15542,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>646.6799999999999</v>
+        <v>62576.9</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>606591-4-CM26</t>
+          <t>606591-5-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15641,13 +15641,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>35616.04</v>
+        <v>32901.72</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>606591-5-CM26</t>
+          <t>606591-4-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15706,7 +15706,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>32901.72</v>
+        <v>35616.04</v>
       </c>
     </row>
     <row r="236">
@@ -15907,7 +15907,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>609685-1-CM26</t>
+          <t>554892-1-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15932,17 +15932,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>53.314.782-8</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15966,13 +15966,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>68515.95</v>
+        <v>61786.7</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>554892-1-CM26</t>
+          <t>609685-1-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15997,17 +15997,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>53.314.782-8</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -16031,7 +16031,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>61786.7</v>
+        <v>68515.95</v>
       </c>
     </row>
     <row r="241">
@@ -16297,7 +16297,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>3378-1718-CM26</t>
+          <t>670784-2-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16322,12 +16322,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -16356,13 +16356,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>17394.98</v>
+        <v>10689.09</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>670784-2-CM26</t>
+          <t>1477-47-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16382,17 +16382,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -16421,13 +16421,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>10689.09</v>
+        <v>37714.34</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1477-47-CM26</t>
+          <t>3378-1718-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16486,7 +16486,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>37714.34</v>
+        <v>17394.98</v>
       </c>
     </row>
     <row r="248">
@@ -16882,7 +16882,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>575437-3-CM26</t>
+          <t>574800-3-SE26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16907,12 +16907,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>60.805.312-3</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16941,13 +16941,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1064847.91</v>
+        <v>716564.4</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>574800-3-SE26</t>
+          <t>575437-3-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16972,12 +16972,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>60.805.312-3</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>716564.4</v>
+        <v>1064847.91</v>
       </c>
     </row>
     <row r="256">
@@ -17597,7 +17597,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1149280-4-SE26</t>
+          <t>1186801-3-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>60.400.000-9</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17656,7 +17656,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>717480.3100000001</v>
+        <v>1205.28</v>
       </c>
     </row>
     <row r="266">
@@ -17727,7 +17727,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1186801-3-CM26</t>
+          <t>1149280-4-SE26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17752,12 +17752,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>60.400.000-9</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17786,7 +17786,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1205.28</v>
+        <v>717480.3100000001</v>
       </c>
     </row>
     <row r="268">
@@ -17987,7 +17987,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1373053-3-CM26</t>
+          <t>603663-54-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -18012,12 +18012,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -18046,7 +18046,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>9257.09</v>
+        <v>76156.3</v>
       </c>
     </row>
     <row r="272">
@@ -18117,7 +18117,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>603663-54-CM26</t>
+          <t>1373053-3-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -18142,12 +18142,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -18176,7 +18176,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>76156.3</v>
+        <v>9257.09</v>
       </c>
     </row>
     <row r="274">
@@ -18247,7 +18247,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1211992-43-CM26</t>
+          <t>4973-40-SE26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18267,17 +18267,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>61.202.016-7</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18306,13 +18306,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1242.65</v>
+        <v>1573308.56</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>4973-40-SE26</t>
+          <t>1211992-43-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18332,17 +18332,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>61.202.016-7</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -18371,7 +18371,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1573308.56</v>
+        <v>1242.65</v>
       </c>
     </row>
     <row r="277">
@@ -18442,7 +18442,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5482-80-CM26</t>
+          <t>5482-81-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18507,7 +18507,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>5482-81-CM26</t>
+          <t>5482-80-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -19092,7 +19092,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1373053-5-CM26</t>
+          <t>1211992-69-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -19112,17 +19112,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -19151,13 +19151,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>9595.75</v>
+        <v>1266.44</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1211992-69-CM26</t>
+          <t>1373053-5-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19177,17 +19177,17 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -19216,7 +19216,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1266.44</v>
+        <v>9595.75</v>
       </c>
     </row>
     <row r="290">
@@ -19742,7 +19742,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1395481-2-SE26</t>
+          <t>1111089-91-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19767,12 +19767,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>60.908.116-3</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19801,13 +19801,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>117272.9</v>
+        <v>160141.93</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1395481-3-SE26</t>
+          <t>1395481-2-SE26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19866,13 +19866,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>257795.23</v>
+        <v>117272.9</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1111089-91-CM26</t>
+          <t>1395481-3-SE26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19897,12 +19897,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.908.116-3</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19931,7 +19931,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>160141.93</v>
+        <v>257795.23</v>
       </c>
     </row>
     <row r="301">
@@ -20327,7 +20327,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>544143-6-CM26</t>
+          <t>1211992-116-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20347,22 +20347,22 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -20386,13 +20386,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>38298.12</v>
+        <v>1405.91</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1211992-116-CM26</t>
+          <t>692264-2-SE26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20412,17 +20412,17 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -20451,13 +20451,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1405.91</v>
+        <v>449847.9</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>692264-2-SE26</t>
+          <t>544143-6-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20482,17 +20482,17 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>449847.9</v>
+        <v>38298.12</v>
       </c>
     </row>
     <row r="310">
@@ -20587,7 +20587,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1422032-52-CM26</t>
+          <t>1515286-3-SE26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20607,22 +20607,22 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>53.337.014-4</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -20646,13 +20646,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>4788.56</v>
+        <v>805575.1800000001</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1515286-3-SE26</t>
+          <t>1422032-52-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20672,22 +20672,22 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>53.337.014-4</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -20711,7 +20711,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>805575.1800000001</v>
+        <v>4788.56</v>
       </c>
     </row>
     <row r="313">
@@ -21172,7 +21172,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1495206-5-CM26</t>
+          <t>1186801-6-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -21197,12 +21197,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -21231,13 +21231,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>3981.12</v>
+        <v>1201.58</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1186801-6-CM26</t>
+          <t>1477-194-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -21262,12 +21262,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -21296,13 +21296,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1201.58</v>
+        <v>36957.96</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1477-194-CM26</t>
+          <t>1495206-5-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21327,12 +21327,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -21361,7 +21361,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>36957.96</v>
+        <v>3981.12</v>
       </c>
     </row>
     <row r="323">
@@ -21887,7 +21887,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>772003-6-SE26</t>
+          <t>772003-7-SE26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21946,13 +21946,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>154472.86</v>
+        <v>19309.11</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>772003-7-SE26</t>
+          <t>772003-6-SE26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -22011,13 +22011,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>19309.11</v>
+        <v>154472.86</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1186801-7-CM26</t>
+          <t>2702-361-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -22042,12 +22042,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -22076,13 +22076,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>1177.97</v>
+        <v>10433.97</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2702-361-CM26</t>
+          <t>1186801-7-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -22107,12 +22107,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -22141,7 +22141,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>10433.97</v>
+        <v>1177.97</v>
       </c>
     </row>
     <row r="335">
@@ -22212,7 +22212,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2701-496-CM26</t>
+          <t>544143-8-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22237,17 +22237,17 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -22271,7 +22271,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>7849.1</v>
+        <v>37139.79</v>
       </c>
     </row>
     <row r="337">
@@ -22342,7 +22342,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>544143-8-CM26</t>
+          <t>2701-496-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22367,17 +22367,17 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -22401,7 +22401,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>37139.79</v>
+        <v>7849.1</v>
       </c>
     </row>
     <row r="339">
@@ -22537,7 +22537,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1211992-168-CM26</t>
+          <t>626802-9-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22557,17 +22557,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>65.034.169-4</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22596,13 +22596,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>1622.04</v>
+        <v>2949.17</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>626802-9-CM26</t>
+          <t>1211992-168-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22622,17 +22622,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>65.034.169-4</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22661,7 +22661,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>2949.17</v>
+        <v>1622.04</v>
       </c>
     </row>
     <row r="343">
@@ -23122,7 +23122,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>670784-10-CM26</t>
+          <t>606591-7-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -23147,12 +23147,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -23181,7 +23181,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>10292.87</v>
+        <v>31368.75</v>
       </c>
     </row>
     <row r="351">
@@ -23252,7 +23252,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>606591-7-CM26</t>
+          <t>670784-10-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23277,12 +23277,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -23311,7 +23311,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>31368.75</v>
+        <v>10292.87</v>
       </c>
     </row>
     <row r="353">
@@ -23382,7 +23382,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>544143-9-CM26</t>
+          <t>1373053-10-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -23407,17 +23407,17 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -23441,13 +23441,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>37448.52</v>
+        <v>9602.950000000001</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1373053-10-CM26</t>
+          <t>544143-9-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23472,17 +23472,17 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -23506,7 +23506,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>9602.950000000001</v>
+        <v>37448.52</v>
       </c>
     </row>
     <row r="356">
@@ -23532,7 +23532,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -23772,7 +23772,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2702-443-CM26</t>
+          <t>2701-649-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23831,13 +23831,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>10270.43</v>
+        <v>7644.2</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2701-649-CM26</t>
+          <t>2702-443-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23896,13 +23896,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>7644.2</v>
+        <v>10270.43</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>558338-4-SE26</t>
+          <t>550716-12-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23927,12 +23927,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23961,13 +23961,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>306084.36</v>
+        <v>6943.58</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>550716-12-CM26</t>
+          <t>558338-4-SE26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -24026,13 +24026,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>6943.58</v>
+        <v>306084.36</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2702-464-CM26</t>
+          <t>1186801-10-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -24057,12 +24057,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -24091,13 +24091,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>10413.64</v>
+        <v>4681.22</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1186801-10-CM26</t>
+          <t>2702-464-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -24122,12 +24122,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -24156,13 +24156,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>4681.22</v>
+        <v>10413.64</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>307-95-CM26</t>
+          <t>2701-677-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24187,12 +24187,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>667.67</v>
+        <v>7594.58</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>307-96-CM26</t>
+          <t>2701-676-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24252,12 +24252,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -24286,13 +24286,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>667.67</v>
+        <v>7594.58</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>307-97-CM26</t>
+          <t>2701-675-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24317,12 +24317,12 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -24351,7 +24351,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>667.67</v>
+        <v>7594.58</v>
       </c>
     </row>
     <row r="369">
@@ -24422,7 +24422,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2701-675-CM26</t>
+          <t>307-97-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -24447,12 +24447,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -24481,13 +24481,13 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>7594.58</v>
+        <v>667.67</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2701-676-CM26</t>
+          <t>307-96-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -24512,12 +24512,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -24546,13 +24546,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>7594.58</v>
+        <v>667.67</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2701-677-CM26</t>
+          <t>307-95-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -24577,12 +24577,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -24611,7 +24611,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>7594.58</v>
+        <v>667.67</v>
       </c>
     </row>
     <row r="373">
@@ -24742,6 +24742,851 @@
       </c>
       <c r="M374" s="2" t="n">
         <v>20926.2</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>4722-5-CM26</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>65.138.650-0</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>DEFENSORIA PENAL PUBLICA</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="n">
+        <v>29037.1</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>544143-11-CM26</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="n">
+        <v>35504.45</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>670784-12-CM26</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>60.818.000-1</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="n">
+        <v>9567.940000000001</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>1211992-203-CM26</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>65.192.585-1</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN YUNUS</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M378" s="2" t="n">
+        <v>1107.44</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>1166422-1-CM26</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>61.001.002-4</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M379" s="2" t="n">
+        <v>73328.53</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>670784-13-CM26</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>60.818.000-1</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M380" s="2" t="n">
+        <v>9756.940000000001</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>670784-14-CM26</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>60.818.000-1</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M381" s="2" t="n">
+        <v>9710.92</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>670784-15-CM26</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>60.818.000-1</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M382" s="2" t="n">
+        <v>9618.870000000001</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>550716-13-CM26</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>65.961.370-0</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M383" s="2" t="n">
+        <v>6673.38</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>1477-321-CM26</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>70.786.200-9</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Corporación de Asistencia Judicial RM</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M384" s="2" t="n">
+        <v>35235.75</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2424-1210-CM26</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>69.061.000-0</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M385" s="2" t="n">
+        <v>536058.01</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>565314-5-SE26</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>61.979.620-9</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M386" s="2" t="n">
+        <v>1222662.99</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>559222-1-CM26</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>60.107.000-6</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M387" s="2" t="n">
+        <v>488295.71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/todos.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/todos.xlsx
@@ -677,7 +677,11 @@
           <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
@@ -738,7 +742,11 @@
           <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
@@ -926,7 +934,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1904,7 +1912,11 @@
           <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
@@ -15797,7 +15809,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -20867,7 +20879,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -21712,7 +21724,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -21777,7 +21789,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
